--- a/pc-web/public/import/importShop.xlsx
+++ b/pc-web/public/import/importShop.xlsx
@@ -129,24 +129,10 @@
 没有暖气费可以和建筑面积填写一样</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>租金一般用在园区，商贸城，商铺等，
-普通小区可以忽略填写0即可</t>
-    </r>
-  </si>
-  <si>
-    <t>业主真实名称，如果房屋存在多个业主时
+    <t>商铺每月租金，如果商铺已经出售不需要组件 那么填写0</t>
+  </si>
+  <si>
+    <t>业主真实名称，如果商铺存在多个业主时
 建议随便写一个，如果物业要求必须要两个
 都需要写时 建议用逗号分隔</t>
   </si>
@@ -172,9 +158,8 @@
 没有时填写 111111111111111111</t>
   </si>
   <si>
-    <t>1001 户主
-1002 户员（成员）
-注意：一个房屋必须要有户主存在 才能 写户员，并且户主要写在 户员之前，每一个户员都需要写一行，前面的房屋信息重复写 不能省略</t>
+    <t xml:space="preserve">1001 户主
+</t>
   </si>
   <si>
     <t>商铺状态</t>
@@ -1635,7 +1620,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" ht="85.5" spans="1:20">
+    <row r="18" ht="28.5" spans="1:20">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
